--- a/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/проективное покрытие в баллах.xlsx
+++ b/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/проективное покрытие в баллах.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$E$25</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1580,6 +1583,9 @@
       <c r="F25" s="7"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E25" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
